--- a/src/frontend/public/templates/advance_template.xlsx
+++ b/src/frontend/public/templates/advance_template.xlsx
@@ -8,19 +8,21 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HuongDan" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data'!$A$1:$F$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,16 +30,75 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="000F172A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos Display"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <i val="1"/>
+      <color rgb="00D1FAE5"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00134E4A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="00334155"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F766E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCFBF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0FDFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,13 +106,56 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -126,6 +230,58 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Codex</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>MST nguoi ban
+Bat buoc
+Nhap dung MST da khai bao tren he thong.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>MST khach hang
+Bat buoc
+MST ben mua hoac ma thue noi bo dang su dung tren he thong.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>So chung tu tra ho
+Bat buoc
+So chung tu bat buoc, dung de chong trung voi du lieu da co.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Ngay tra ho
+Bat buoc
+Ngay lap chung tu tra ho. Ho tro yyyy-MM-dd, dd/MM/yyyy, dd-MM-yyyy.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>So tien
+Bat buoc
+Gia tri tra ho. Phai lon hon 0.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Dien giai
+Tuy chon
+Mo ta nghiep vu, chi phi, nguon phat sinh.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -414,63 +570,363 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000F766E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>seller_tax_code</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>customer_tax_code</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>advance_no</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>advance_date</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2300328765</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>0101000002</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>TH-2026-0001</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Tra ho cuoc van chuyen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0014B8A6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Template import Khoan tra ho KH</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>So chung tu la bat buoc va duoc dung de doi soat trung tren he thong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Nguyen tac chung</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>- Sheet Data la sheet import chinh. Dong 1 la header co dinh, dong 2 la dong mau de tham chieu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>- Khong doi ten header. Co the thay doi thu tu cot, nhung khuyen nghi giu nguyen de doi soat noi bo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>- Ngay chap nhan: yyyy-MM-dd, dd/MM/yyyy, dd-MM-yyyy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>- Dong co loi se khong duoc ghi so. Dong canh bao co the bi bo qua tuy theo quy tac import.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Quy tac chong trung</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>He thong doi chieu trung theo seller_tax_code + customer_tax_code + advance_no.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Luu y nghiep vu</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>- Neu trung so chung tu voi ban ghi dang ton tai, dong import se bi canh bao va bo qua.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Mo ta tung cot</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Cot trong file</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Bat buoc</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Y nghia</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>Vi du</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>seller_tax_code</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Nhap dung MST da khai bao tren he thong.</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>2300328765</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>customer_tax_code</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>MST ben mua hoac ma thue noi bo dang su dung tren he thong.</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>0101000002</t>
         </is>
       </c>
-      <c r="C2" s="1" t="n">
-        <v>46023</v>
-      </c>
-      <c r="D2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Tam ung cong no</t>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>advance_no</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>So chung tu bat buoc, dung de chong trung voi du lieu da co.</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>TH-2026-0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>advance_date</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Ngay lap chung tu tra ho. Ho tro yyyy-MM-dd, dd/MM/yyyy, dd-MM-yyyy.</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Co</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Gia tri tra ho. Phai lon hon 0.</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>1500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Khong</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Mo ta nghiep vu, chi phi, nguon phat sinh.</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Tra ho cuoc van chuyen</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>